--- a/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
@@ -62408,13 +62408,13 @@
         <v>0</v>
       </c>
       <c r="AW284" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX284" t="n">
         <v>4</v>
       </c>
       <c r="AY284" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ284" t="n">
         <v>4</v>
@@ -62847,13 +62847,13 @@
         <v>8</v>
       </c>
       <c r="AX286" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY286" t="n">
         <v>13</v>
       </c>
       <c r="AZ286" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA286" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP288"/>
+  <dimension ref="A1:BP289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.36</v>
@@ -7454,7 +7454,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR32" t="n">
         <v>1.7</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.07</v>
@@ -12904,7 +12904,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR57" t="n">
         <v>1.48</v>
@@ -13337,7 +13337,7 @@
         <v>2.33</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.53</v>
@@ -15956,7 +15956,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR71" t="n">
         <v>2.44</v>
@@ -18787,7 +18787,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.21</v>
@@ -20970,7 +20970,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR94" t="n">
         <v>1.65</v>
@@ -22275,7 +22275,7 @@
         <v>0.8</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.93</v>
@@ -25984,7 +25984,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR117" t="n">
         <v>1.8</v>
@@ -29472,7 +29472,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR133" t="n">
         <v>1.74</v>
@@ -29905,7 +29905,7 @@
         <v>1.67</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.36</v>
@@ -33614,7 +33614,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR152" t="n">
         <v>1.69</v>
@@ -35573,7 +35573,7 @@
         <v>1.86</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.93</v>
@@ -37538,7 +37538,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR170" t="n">
         <v>1.73</v>
@@ -38407,7 +38407,7 @@
         <v>1.38</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.53</v>
@@ -43203,7 +43203,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ196" t="n">
         <v>0.57</v>
@@ -44078,7 +44078,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR200" t="n">
         <v>1.43</v>
@@ -49746,7 +49746,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR226" t="n">
         <v>1.25</v>
@@ -51054,7 +51054,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR232" t="n">
         <v>1.85</v>
@@ -58681,7 +58681,7 @@
         <v>1.31</v>
       </c>
       <c r="AP267" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ267" t="n">
         <v>1.43</v>
@@ -59774,7 +59774,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR272" t="n">
         <v>2.31</v>
@@ -60643,7 +60643,7 @@
         <v>0.62</v>
       </c>
       <c r="AP276" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ276" t="n">
         <v>0.64</v>
@@ -62605,7 +62605,7 @@
         <v>1.36</v>
       </c>
       <c r="AP285" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ285" t="n">
         <v>1.47</v>
@@ -63274,13 +63274,13 @@
         <v>3.56</v>
       </c>
       <c r="AU288" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV288" t="n">
         <v>9</v>
       </c>
       <c r="AW288" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX288" t="n">
         <v>10</v>
@@ -63338,6 +63338,224 @@
       </c>
       <c r="BP288" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>7957585</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>46083.66666666666</v>
+      </c>
+      <c r="F289" t="n">
+        <v>26</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Utrecht II</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>1</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R289" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S289" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T289" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U289" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V289" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W289" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X289" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI289" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ289" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS289" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT289" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AU289" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX289" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY289" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ289" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA289" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB289" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC289" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD289" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE289" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF289" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG289" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH289" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BI289" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ289" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK289" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL289" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM289" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN289" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO289" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP289" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP289"/>
+  <dimension ref="A1:BP290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.07</v>
@@ -3966,7 +3966,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -8326,7 +8326,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR36" t="n">
         <v>1.13</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.2</v>
@@ -8977,7 +8977,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.47</v>
@@ -13994,7 +13994,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR62" t="n">
         <v>2.29</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.43</v>
@@ -17700,7 +17700,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR79" t="n">
         <v>2.49</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.79</v>
@@ -21406,7 +21406,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR96" t="n">
         <v>1.47</v>
@@ -22493,7 +22493,7 @@
         <v>1.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.67</v>
@@ -25112,7 +25112,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR113" t="n">
         <v>1.74</v>
@@ -29687,7 +29687,7 @@
         <v>0.33</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.64</v>
@@ -30780,7 +30780,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR139" t="n">
         <v>1.62</v>
@@ -33832,7 +33832,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR153" t="n">
         <v>1.76</v>
@@ -34483,7 +34483,7 @@
         <v>2.71</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ156" t="n">
         <v>2.43</v>
@@ -37753,7 +37753,7 @@
         <v>0.5</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.57</v>
@@ -38628,7 +38628,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR175" t="n">
         <v>1.42</v>
@@ -39933,7 +39933,7 @@
         <v>1.33</v>
       </c>
       <c r="AP181" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ181" t="n">
         <v>1</v>
@@ -42770,7 +42770,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR194" t="n">
         <v>1.67</v>
@@ -44729,7 +44729,7 @@
         <v>0.9</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ203" t="n">
         <v>0.8</v>
@@ -51272,7 +51272,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR233" t="n">
         <v>1.64</v>
@@ -53888,7 +53888,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR245" t="n">
         <v>1.3</v>
@@ -59335,7 +59335,7 @@
         <v>1.38</v>
       </c>
       <c r="AP270" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ270" t="n">
         <v>1.36</v>
@@ -59992,7 +59992,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR273" t="n">
         <v>1.4</v>
@@ -60861,7 +60861,7 @@
         <v>1.08</v>
       </c>
       <c r="AP277" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ277" t="n">
         <v>0.93</v>
@@ -63262,7 +63262,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ288" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR288" t="n">
         <v>1.78</v>
@@ -63556,6 +63556,224 @@
       </c>
       <c r="BP289" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>7957593</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>46084.66666666666</v>
+      </c>
+      <c r="F290" t="n">
+        <v>26</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" t="n">
+        <v>2</v>
+      </c>
+      <c r="L290" t="n">
+        <v>3</v>
+      </c>
+      <c r="M290" t="n">
+        <v>2</v>
+      </c>
+      <c r="N290" t="n">
+        <v>5</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>['35', '47', '64']</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>['24', '86']</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R290" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S290" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T290" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U290" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="V290" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W290" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X290" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO290" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP290" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AQ290" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR290" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS290" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT290" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AU290" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY290" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ290" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA290" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB290" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC290" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD290" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE290" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF290" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BG290" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH290" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="BI290" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ290" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK290" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL290" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM290" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN290" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO290" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP290" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP290"/>
+  <dimension ref="A1:BP296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.93</v>
@@ -1132,7 +1132,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.93</v>
@@ -1568,7 +1568,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.93</v>
@@ -2658,7 +2658,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.67</v>
@@ -4620,7 +4620,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.79</v>
@@ -5056,7 +5056,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR21" t="n">
         <v>2.92</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.47</v>
@@ -5489,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR23" t="n">
         <v>0.86</v>
@@ -5707,10 +5707,10 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR24" t="n">
         <v>1.79</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.93</v>
@@ -6582,7 +6582,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR28" t="n">
         <v>1.04</v>
@@ -7233,7 +7233,7 @@
         <v>3</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.93</v>
@@ -7890,7 +7890,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR34" t="n">
         <v>1.43</v>
@@ -9195,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR40" t="n">
         <v>1.71</v>
@@ -9852,7 +9852,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR43" t="n">
         <v>1.38</v>
@@ -10503,10 +10503,10 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR46" t="n">
         <v>1.13</v>
@@ -10939,10 +10939,10 @@
         <v>3</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR48" t="n">
         <v>1.86</v>
@@ -11157,7 +11157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.57</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.53</v>
@@ -11814,7 +11814,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR52" t="n">
         <v>1.76</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.93</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.93</v>
@@ -13119,7 +13119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.07</v>
@@ -13555,10 +13555,10 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR60" t="n">
         <v>1.79</v>
@@ -13776,7 +13776,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR61" t="n">
         <v>1.61</v>
@@ -14427,10 +14427,10 @@
         <v>1.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR64" t="n">
         <v>1.93</v>
@@ -15302,7 +15302,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR68" t="n">
         <v>1.93</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.93</v>
@@ -15738,7 +15738,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ70" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR70" t="n">
         <v>1.36</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.93</v>
@@ -16389,7 +16389,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.67</v>
@@ -17918,7 +17918,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR80" t="n">
         <v>1.22</v>
@@ -18133,7 +18133,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.93</v>
@@ -18354,7 +18354,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR82" t="n">
         <v>1.58</v>
@@ -19223,7 +19223,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.53</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -19880,7 +19880,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR89" t="n">
         <v>1.96</v>
@@ -20095,7 +20095,7 @@
         <v>0.75</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.2</v>
@@ -21188,7 +21188,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR95" t="n">
         <v>1.42</v>
@@ -21403,7 +21403,7 @@
         <v>0.75</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.27</v>
@@ -21624,7 +21624,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ97" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR97" t="n">
         <v>1.57</v>
@@ -22057,7 +22057,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.21</v>
@@ -22929,7 +22929,7 @@
         <v>1.25</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.21</v>
@@ -23147,7 +23147,7 @@
         <v>0.6</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.79</v>
@@ -23365,7 +23365,7 @@
         <v>2</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.93</v>
@@ -23586,7 +23586,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR106" t="n">
         <v>1.55</v>
@@ -23804,7 +23804,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR107" t="n">
         <v>1.55</v>
@@ -24237,7 +24237,7 @@
         <v>1.8</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ109" t="n">
         <v>1</v>
@@ -24455,7 +24455,7 @@
         <v>1</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.53</v>
@@ -24894,7 +24894,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR112" t="n">
         <v>1.62</v>
@@ -25109,7 +25109,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.27</v>
@@ -25327,10 +25327,10 @@
         <v>1.4</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR114" t="n">
         <v>1.79</v>
@@ -25981,7 +25981,7 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.93</v>
@@ -26420,7 +26420,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR119" t="n">
         <v>1.55</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.53</v>
@@ -27071,7 +27071,7 @@
         <v>0.6</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.2</v>
@@ -27292,7 +27292,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR123" t="n">
         <v>2.48</v>
@@ -28161,7 +28161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.53</v>
@@ -28600,7 +28600,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR129" t="n">
         <v>1.58</v>
@@ -29033,7 +29033,7 @@
         <v>1.33</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.21</v>
@@ -29469,7 +29469,7 @@
         <v>0.5</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.93</v>
@@ -29690,7 +29690,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR134" t="n">
         <v>2.04</v>
@@ -29908,7 +29908,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR135" t="n">
         <v>1.94</v>
@@ -30126,7 +30126,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ136" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR136" t="n">
         <v>1.34</v>
@@ -30777,7 +30777,7 @@
         <v>0.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.27</v>
@@ -30995,10 +30995,10 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR140" t="n">
         <v>2.07</v>
@@ -31431,7 +31431,7 @@
         <v>1.29</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ142" t="n">
         <v>1</v>
@@ -32739,10 +32739,10 @@
         <v>1.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR148" t="n">
         <v>1.37</v>
@@ -33175,7 +33175,7 @@
         <v>1.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.93</v>
@@ -34047,7 +34047,7 @@
         <v>1.38</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.47</v>
@@ -34265,7 +34265,7 @@
         <v>1.57</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.21</v>
@@ -34486,7 +34486,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ156" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR156" t="n">
         <v>1.96</v>
@@ -34704,7 +34704,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR157" t="n">
         <v>1.48</v>
@@ -35791,7 +35791,7 @@
         <v>1.29</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.2</v>
@@ -36227,10 +36227,10 @@
         <v>0.29</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR164" t="n">
         <v>1.46</v>
@@ -36881,7 +36881,7 @@
         <v>1.5</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.53</v>
@@ -37102,7 +37102,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR168" t="n">
         <v>1.65</v>
@@ -37320,7 +37320,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR169" t="n">
         <v>1.82</v>
@@ -37535,7 +37535,7 @@
         <v>0.63</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.93</v>
@@ -38189,10 +38189,10 @@
         <v>2.38</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ173" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR173" t="n">
         <v>2</v>
@@ -39282,7 +39282,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR178" t="n">
         <v>1.7</v>
@@ -40151,10 +40151,10 @@
         <v>0.67</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR182" t="n">
         <v>1.41</v>
@@ -40369,10 +40369,10 @@
         <v>1.56</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR183" t="n">
         <v>1.17</v>
@@ -40805,7 +40805,7 @@
         <v>1.22</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.53</v>
@@ -41241,10 +41241,10 @@
         <v>0.25</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR187" t="n">
         <v>2.04</v>
@@ -42116,7 +42116,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR191" t="n">
         <v>1.75</v>
@@ -42552,7 +42552,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ193" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR193" t="n">
         <v>1.42</v>
@@ -43424,7 +43424,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR197" t="n">
         <v>1.25</v>
@@ -43639,7 +43639,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.93</v>
@@ -44293,7 +44293,7 @@
         <v>1.5</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.53</v>
@@ -44514,7 +44514,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR202" t="n">
         <v>2.41</v>
@@ -44732,7 +44732,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ203" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR203" t="n">
         <v>1.76</v>
@@ -44947,7 +44947,7 @@
         <v>1.4</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.53</v>
@@ -45383,7 +45383,7 @@
         <v>1</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.79</v>
@@ -45819,7 +45819,7 @@
         <v>1.4</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ208" t="n">
         <v>1.47</v>
@@ -46040,7 +46040,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR209" t="n">
         <v>1.52</v>
@@ -46476,7 +46476,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR211" t="n">
         <v>1.48</v>
@@ -46691,7 +46691,7 @@
         <v>1.2</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.21</v>
@@ -47127,7 +47127,7 @@
         <v>1.27</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.53</v>
@@ -47566,7 +47566,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR216" t="n">
         <v>1.8</v>
@@ -47781,7 +47781,7 @@
         <v>1.82</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ217" t="n">
         <v>1.67</v>
@@ -48217,7 +48217,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ219" t="n">
         <v>1.47</v>
@@ -48656,7 +48656,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR221" t="n">
         <v>1.69</v>
@@ -48871,7 +48871,7 @@
         <v>1.1</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.07</v>
@@ -49092,7 +49092,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ223" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR223" t="n">
         <v>1.67</v>
@@ -49310,7 +49310,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR224" t="n">
         <v>2.48</v>
@@ -49525,7 +49525,7 @@
         <v>1.2</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ225" t="n">
         <v>1</v>
@@ -50615,7 +50615,7 @@
         <v>1.36</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ230" t="n">
         <v>1.2</v>
@@ -51487,7 +51487,7 @@
         <v>1.83</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.93</v>
@@ -51923,10 +51923,10 @@
         <v>1</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ236" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR236" t="n">
         <v>1.29</v>
@@ -52795,7 +52795,7 @@
         <v>1.67</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ240" t="n">
         <v>1.67</v>
@@ -54103,7 +54103,7 @@
         <v>0.45</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ246" t="n">
         <v>0.57</v>
@@ -54542,7 +54542,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ248" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR248" t="n">
         <v>2.33</v>
@@ -54757,7 +54757,7 @@
         <v>1.08</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ249" t="n">
         <v>1</v>
@@ -54978,7 +54978,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR250" t="n">
         <v>1.27</v>
@@ -55193,10 +55193,10 @@
         <v>2.27</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ251" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR251" t="n">
         <v>1.77</v>
@@ -55411,7 +55411,7 @@
         <v>1.27</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ252" t="n">
         <v>0.93</v>
@@ -55632,7 +55632,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR253" t="n">
         <v>1.91</v>
@@ -56722,7 +56722,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ258" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR258" t="n">
         <v>2.38</v>
@@ -57373,7 +57373,7 @@
         <v>0.85</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ261" t="n">
         <v>0.79</v>
@@ -57591,7 +57591,7 @@
         <v>0.42</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ262" t="n">
         <v>0.57</v>
@@ -58463,7 +58463,7 @@
         <v>1.08</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ266" t="n">
         <v>1.07</v>
@@ -58684,7 +58684,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR267" t="n">
         <v>1.77</v>
@@ -58899,10 +58899,10 @@
         <v>0.42</v>
       </c>
       <c r="AP268" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR268" t="n">
         <v>1.74</v>
@@ -59117,10 +59117,10 @@
         <v>2.33</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ269" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR269" t="n">
         <v>1.44</v>
@@ -59338,7 +59338,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR270" t="n">
         <v>1.83</v>
@@ -59989,7 +59989,7 @@
         <v>1.33</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ273" t="n">
         <v>1.27</v>
@@ -60207,10 +60207,10 @@
         <v>0.86</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ274" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR274" t="n">
         <v>1.71</v>
@@ -60646,7 +60646,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ276" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR276" t="n">
         <v>1.86</v>
@@ -61082,7 +61082,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ278" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AR278" t="n">
         <v>1.86</v>
@@ -63774,6 +63774,1314 @@
       </c>
       <c r="BP290" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>7957636</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F291" t="n">
+        <v>30</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Roda JC</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>PSV II</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>1</v>
+      </c>
+      <c r="K291" t="n">
+        <v>1</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
+        <v>2</v>
+      </c>
+      <c r="N291" t="n">
+        <v>2</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>['36', '70']</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R291" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S291" t="n">
+        <v>5</v>
+      </c>
+      <c r="T291" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U291" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V291" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W291" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X291" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AO291" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP291" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ291" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR291" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS291" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT291" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AU291" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV291" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW291" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX291" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY291" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ291" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA291" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB291" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC291" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD291" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE291" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF291" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BG291" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH291" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI291" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ291" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK291" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL291" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM291" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN291" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO291" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BP291" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>7957627</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F292" t="n">
+        <v>30</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Dordrecht</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>MVV</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>1</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1</v>
+      </c>
+      <c r="K292" t="n">
+        <v>2</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" t="n">
+        <v>1</v>
+      </c>
+      <c r="N292" t="n">
+        <v>2</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R292" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S292" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T292" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U292" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V292" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W292" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X292" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI292" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK292" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN292" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO292" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP292" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ292" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS292" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT292" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU292" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV292" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW292" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX292" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY292" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ292" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA292" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB292" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC292" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD292" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE292" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF292" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG292" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH292" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI292" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ292" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK292" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL292" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM292" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN292" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO292" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP292" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>7957628</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F293" t="n">
+        <v>30</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Ajax II</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>1</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>1</v>
+      </c>
+      <c r="L293" t="n">
+        <v>2</v>
+      </c>
+      <c r="M293" t="n">
+        <v>1</v>
+      </c>
+      <c r="N293" t="n">
+        <v>3</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>['26', '66']</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R293" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S293" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T293" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U293" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V293" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W293" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X293" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AK293" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM293" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN293" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO293" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP293" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ293" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR293" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS293" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT293" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU293" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV293" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW293" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX293" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY293" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ293" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA293" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB293" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC293" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD293" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE293" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF293" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG293" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH293" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI293" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ293" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK293" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL293" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM293" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN293" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO293" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP293" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>7957635</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F294" t="n">
+        <v>30</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Helmond Sport</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Oss</t>
+        </is>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="n">
+        <v>1</v>
+      </c>
+      <c r="M294" t="n">
+        <v>1</v>
+      </c>
+      <c r="N294" t="n">
+        <v>2</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R294" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S294" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T294" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U294" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V294" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W294" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X294" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI294" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK294" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN294" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO294" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP294" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ294" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR294" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS294" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT294" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU294" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW294" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX294" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY294" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ294" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA294" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB294" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC294" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD294" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE294" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF294" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG294" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH294" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI294" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ294" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK294" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL294" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM294" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN294" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO294" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BP294" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>7957637</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F295" t="n">
+        <v>30</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>VVV</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
+        <v>3</v>
+      </c>
+      <c r="N295" t="n">
+        <v>3</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>['62', '67', '76']</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R295" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S295" t="n">
+        <v>3</v>
+      </c>
+      <c r="T295" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U295" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V295" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W295" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X295" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN295" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO295" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP295" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ295" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS295" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT295" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AU295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV295" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW295" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX295" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY295" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ295" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA295" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB295" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC295" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD295" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE295" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF295" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG295" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH295" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI295" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ295" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK295" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL295" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM295" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN295" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO295" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP295" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>7957615</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>46088.52083333334</v>
+      </c>
+      <c r="F296" t="n">
+        <v>30</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="n">
+        <v>1</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R296" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S296" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T296" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U296" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V296" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W296" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X296" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN296" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO296" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP296" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ296" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AR296" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS296" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT296" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AU296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV296" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW296" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY296" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ296" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA296" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB296" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC296" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD296" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BE296" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF296" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BG296" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH296" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="BI296" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ296" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BK296" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL296" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM296" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN296" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO296" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP296" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eerste Divisie_20252026.xlsx
@@ -65021,19 +65021,19 @@
         <v>2</v>
       </c>
       <c r="AV296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW296" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX296" t="n">
         <v>4</v>
       </c>
       <c r="AY296" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ296" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA296" t="n">
         <v>3</v>
